--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67699746</v>
+        <v>136177267</v>
       </c>
       <c r="B17" t="n">
-        <v>5199</v>
+        <v>4783</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,42 +2416,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tandagneten, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>639314</v>
+        <v>639263</v>
       </c>
       <c r="R17" t="n">
-        <v>6668190</v>
+        <v>6668154</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,12 +2470,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,78 +2497,93 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>äldre, grovstammig barrskog</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>död gran</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699746</t>
+          <t>https://artportalen.se/Sighting/136177267</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>67699758</v>
+        <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>58143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tandagneten, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>639347</v>
+        <v>639294</v>
       </c>
       <c r="R18" t="n">
-        <v>6668107</v>
+        <v>6668155</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,12 +2607,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,74 +2633,74 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>äldre, grovstammig barrskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699758</t>
+          <t>https://artportalen.se/Sighting/136177268</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67699756</v>
+        <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>106244</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tandagneten, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>639329</v>
+        <v>639321</v>
       </c>
       <c r="R19" t="n">
-        <v>6668297</v>
+        <v>6668100</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2694,12 +2724,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,71 +2750,71 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>äldre, grovstammig barrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699756</t>
+          <t>https://artportalen.se/Sighting/136177271</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67699738</v>
+        <v>67699746</v>
       </c>
       <c r="B20" t="n">
-        <v>91930</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>639377</v>
+        <v>639314</v>
       </c>
       <c r="R20" t="n">
-        <v>6668399</v>
+        <v>6668190</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2865,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>död gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2842,38 +2882,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699738</t>
+          <t>https://artportalen.se/Sighting/67699746</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67699739</v>
+        <v>67699758</v>
       </c>
       <c r="B21" t="n">
-        <v>91930</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2883,10 +2923,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>639377</v>
+        <v>639347</v>
       </c>
       <c r="R21" t="n">
-        <v>6668376</v>
+        <v>6668107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,11 +2975,6 @@
           <t>äldre, grovstammig barrskog</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>gammal tall</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -2954,38 +2989,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699739</t>
+          <t>https://artportalen.se/Sighting/67699758</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67699740</v>
+        <v>67699756</v>
       </c>
       <c r="B22" t="n">
-        <v>91930</v>
+        <v>106244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +3030,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>639295</v>
+        <v>639329</v>
       </c>
       <c r="R22" t="n">
-        <v>6668342</v>
+        <v>6668297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,11 +3082,6 @@
           <t>äldre, grovstammig barrskog</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>gammal tall</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3066,16 +3096,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699740</t>
+          <t>https://artportalen.se/Sighting/67699756</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67699753</v>
+        <v>67699738</v>
       </c>
       <c r="B23" t="n">
-        <v>5178</v>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,39 +3113,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102204</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>639370</v>
+        <v>639377</v>
       </c>
       <c r="R23" t="n">
-        <v>6668430</v>
+        <v>6668399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3191,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3183,56 +3208,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699753</t>
+          <t>https://artportalen.se/Sighting/67699738</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67699752</v>
+        <v>67699739</v>
       </c>
       <c r="B24" t="n">
-        <v>4781</v>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>639348</v>
+        <v>639377</v>
       </c>
       <c r="R24" t="n">
-        <v>6668448</v>
+        <v>6668376</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,7 +3303,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3300,56 +3320,51 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699752</t>
+          <t>https://artportalen.se/Sighting/67699739</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67699755</v>
+        <v>67699740</v>
       </c>
       <c r="B25" t="n">
-        <v>4781</v>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>639336</v>
+        <v>639295</v>
       </c>
       <c r="R25" t="n">
-        <v>6668343</v>
+        <v>6668342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,7 +3415,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3417,51 +3432,56 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699755</t>
+          <t>https://artportalen.se/Sighting/67699740</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67699737</v>
+        <v>67699753</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>5178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>102204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>639364</v>
+        <v>639370</v>
       </c>
       <c r="R26" t="n">
-        <v>6668404</v>
+        <v>6668430</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,6 +3530,11 @@
           <t>äldre, grovstammig barrskog</t>
         </is>
       </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3524,51 +3549,56 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699737</t>
+          <t>https://artportalen.se/Sighting/67699753</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67699754</v>
+        <v>67699752</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>4781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639370</v>
+        <v>639348</v>
       </c>
       <c r="R27" t="n">
-        <v>6668430</v>
+        <v>6668448</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3617,6 +3647,11 @@
           <t>äldre, grovstammig barrskog</t>
         </is>
       </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3631,16 +3666,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699754</t>
+          <t>https://artportalen.se/Sighting/67699752</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67699741</v>
+        <v>67699755</v>
       </c>
       <c r="B28" t="n">
-        <v>106244</v>
+        <v>4781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,34 +3683,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>639369</v>
+        <v>639336</v>
       </c>
       <c r="R28" t="n">
-        <v>6668310</v>
+        <v>6668343</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,6 +3764,11 @@
           <t>äldre, grovstammig barrskog</t>
         </is>
       </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3738,58 +3783,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67699741</t>
+          <t>https://artportalen.se/Sighting/67699755</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>68300843</v>
+        <v>67699737</v>
       </c>
       <c r="B29" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tandagneten, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>639365</v>
+        <v>639364</v>
       </c>
       <c r="R29" t="n">
-        <v>6668314</v>
+        <v>6668404</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,17 +3854,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-11-10</t>
+          <t>2017-08-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-11-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Två grupper med flera skott</t>
+          <t>2017-08-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,62 +3871,57 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Hedbarrskog</t>
-        </is>
-      </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Åsbarrskog med grövre tallöverståndare</t>
+          <t>äldre, grovstammig barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Sundberg</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Sundberg</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68300843</t>
+          <t>https://artportalen.se/Sighting/67699737</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67699742</v>
+        <v>67699754</v>
       </c>
       <c r="B30" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3903,10 +3931,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>639365</v>
+        <v>639370</v>
       </c>
       <c r="R30" t="n">
-        <v>6668314</v>
+        <v>6668430</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3968,6 +3996,344 @@
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67699754</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>67699741</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tandagneten, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>639369</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6668310</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre, grovstammig barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67699741</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>68300843</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tandagneten, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>639365</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6668314</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2017-11-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2017-11-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Två grupper med flera skott</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Hedbarrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Åsbarrskog med grövre tallöverståndare</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68300843</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>67699742</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tandagneten, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>639365</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6668314</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>äldre, grovstammig barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67699742</t>
         </is>
@@ -4004,6 +4370,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
